--- a/artfynd/A 46735-2024 artfynd.xlsx
+++ b/artfynd/A 46735-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,117 +1155,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>114700434</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>656107</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6657857</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Rasbokil</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>C-Upp-0985</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2016-10-16</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2016-10-16</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
